--- a/templates/teachers.xlsx
+++ b/templates/teachers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Professeurs" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,45 +397,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Matricule</v>
+      </c>
+      <c r="B1" t="str">
         <v>Nom*</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Prénom*</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Type*</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Matières*</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Taux horaire FCFA</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Salaire mensuel FCFA</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Diallo</v>
+        <v>TCH-P-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Ibrahim</v>
+        <v>Exemple</v>
       </c>
       <c r="C2" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="D2" t="str">
+        <v>permanent</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Mathématiques</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TCH-V-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Exemple</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Vacataire</v>
+      </c>
+      <c r="D3" t="str">
         <v>vacataire</v>
       </c>
-      <c r="D2" t="str">
-        <v>Mathématiques, Physique</v>
-      </c>
-      <c r="E2" t="str">
-        <v>5000</v>
+      <c r="E3" t="str">
+        <v>Anglais</v>
+      </c>
+      <c r="F3" t="str">
+        <v>9000</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>